--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="정예은" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="윤서희" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="정진아" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="이수민" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="나시은" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="문희선" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="문희선" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="예윤진" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -261,10 +261,10 @@
     <t xml:space="preserve">디자이너</t>
   </si>
   <si>
-    <t xml:space="preserve">나시은</t>
-  </si>
-  <si>
     <t xml:space="preserve">문희선</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예윤진</t>
   </si>
 </sst>
 </file>
@@ -969,9 +969,11 @@
   <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.78"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="9"/>
   </cols>
   <sheetData>
@@ -2085,9 +2087,11 @@
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3188,9 +3192,11 @@
   <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.87"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="9"/>
   </cols>
   <sheetData>
@@ -4305,9 +4311,11 @@
   <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,9 +5428,11 @@
   <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,9 +6545,11 @@
   <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="8.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="8.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
